--- a/TalkTukTuk_Phrases.xlsx
+++ b/TalkTukTuk_Phrases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TOSHIBA\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B45470FE-474D-478A-B97B-DA0B1743341D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D8BDF50-4C54-4194-9DE8-6316D0798F50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5115" yWindow="1005" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Phrases" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="288">
   <si>
     <t>PhraseID</t>
   </si>
@@ -869,13 +869,28 @@
   </si>
   <si>
     <t>https://raw.githubusercontent.com/Mickalacki/talktuktuk/main/PHR-COL-008.mp4</t>
+  </si>
+  <si>
+    <t>PHR-SOC-006</t>
+  </si>
+  <si>
+    <t>You are handsome</t>
+  </si>
+  <si>
+    <t>អ្នកសង្ហាណាស់</t>
+  </si>
+  <si>
+    <t>Neak Songha Nas</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Mickalacki/talktuktuk/main/PHR-SOC-006.mp4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -894,6 +909,14 @@
       <sz val="11"/>
       <color rgb="FF1565C0"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="10">
@@ -953,10 +976,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1003,8 +1027,12 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1305,13 +1333,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="4" width="25" customWidth="1"/>
-    <col min="5" max="5" width="70" customWidth="1"/>
+    <col min="5" max="5" width="77.85546875" customWidth="1"/>
     <col min="6" max="7" width="15" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
   </cols>
@@ -2019,46 +2047,46 @@
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="F28" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="G28" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="H28" s="10" t="s">
+      <c r="A28" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="H28" s="8" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>152</v>
@@ -2072,19 +2100,19 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="F30" s="10" t="s">
         <v>152</v>
@@ -2098,19 +2126,19 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>152</v>
@@ -2124,19 +2152,19 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F32" s="10" t="s">
         <v>152</v>
@@ -2150,19 +2178,19 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>152</v>
@@ -2176,19 +2204,19 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="F34" s="10" t="s">
         <v>152</v>
@@ -2202,19 +2230,19 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>152</v>
@@ -2228,19 +2256,19 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F36" s="10" t="s">
         <v>152</v>
@@ -2254,19 +2282,19 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>152</v>
@@ -2279,46 +2307,46 @@
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="12" t="s">
-        <v>199</v>
-      </c>
-      <c r="B38" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="C38" s="12" t="s">
-        <v>201</v>
-      </c>
-      <c r="D38" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="E38" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="F38" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="G38" s="12" t="s">
-        <v>205</v>
-      </c>
-      <c r="H38" s="12" t="s">
+      <c r="A38" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="G38" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="H38" s="10" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="F39" s="12" t="s">
         <v>204</v>
@@ -2332,19 +2360,19 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="F40" s="12" t="s">
         <v>204</v>
@@ -2358,19 +2386,19 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="F41" s="12" t="s">
         <v>204</v>
@@ -2384,19 +2412,19 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="F42" s="12" t="s">
         <v>204</v>
@@ -2410,19 +2438,19 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="F43" s="12" t="s">
         <v>204</v>
@@ -2436,19 +2464,19 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F44" s="12" t="s">
         <v>204</v>
@@ -2462,19 +2490,19 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="F45" s="12" t="s">
         <v>204</v>
@@ -2487,46 +2515,46 @@
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="14" t="s">
-        <v>241</v>
-      </c>
-      <c r="B46" s="14" t="s">
-        <v>242</v>
-      </c>
-      <c r="C46" s="14" t="s">
-        <v>243</v>
-      </c>
-      <c r="D46" s="14" t="s">
-        <v>244</v>
-      </c>
-      <c r="E46" s="15" t="s">
-        <v>245</v>
-      </c>
-      <c r="F46" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="G46" s="14" t="s">
-        <v>247</v>
-      </c>
-      <c r="H46" s="14" t="s">
+      <c r="A46" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="C46" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="E46" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="F46" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="G46" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="H46" s="12" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="14" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="E47" s="15" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="F47" s="14" t="s">
         <v>246</v>
@@ -2540,19 +2568,19 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="14" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E48" s="15" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F48" s="14" t="s">
         <v>246</v>
@@ -2566,19 +2594,19 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="14" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="E49" s="15" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="F49" s="14" t="s">
         <v>246</v>
@@ -2592,19 +2620,19 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="14" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B50" s="14" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="F50" s="14" t="s">
         <v>246</v>
@@ -2618,19 +2646,19 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="14" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="E51" s="15" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="F51" s="14" t="s">
         <v>246</v>
@@ -2644,19 +2672,19 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="14" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="B52" s="14" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="F52" s="14" t="s">
         <v>246</v>
@@ -2670,19 +2698,19 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="14" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="B53" s="14" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="E53" s="15" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="F53" s="14" t="s">
         <v>246</v>
@@ -2694,7 +2722,36 @@
         <v>15</v>
       </c>
     </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="B54" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="C54" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="D54" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="E54" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="F54" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="G54" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="H54" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E28" r:id="rId1" xr:uid="{9D7F697B-04A3-43D8-834D-1DD935D30A27}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/TalkTukTuk_Phrases.xlsx
+++ b/TalkTukTuk_Phrases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TOSHIBA\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4327ECA5-66AC-4F91-B102-EFC981836DF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AD88810-1231-4A12-A487-F436FDA2E319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="405" yWindow="765" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Phrases" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="293">
   <si>
     <t>PhraseID</t>
   </si>
@@ -884,6 +884,21 @@
   </si>
   <si>
     <t>https://raw.githubusercontent.com/Mickalacki/talktuktuk/main/PHR-SOC-006.mp4</t>
+  </si>
+  <si>
+    <t>PHR-DAY-009</t>
+  </si>
+  <si>
+    <t>Day</t>
+  </si>
+  <si>
+    <t>ថ្ងៃ</t>
+  </si>
+  <si>
+    <t>Kani</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Mickalacki/talktuktuk/main/PHR-DAY-009.mp4</t>
   </si>
 </sst>
 </file>
@@ -980,7 +995,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1028,6 +1043,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1333,7 +1351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -2527,7 +2545,7 @@
       <c r="D46" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="E46" s="13" t="s">
+      <c r="E46" s="17" t="s">
         <v>240</v>
       </c>
       <c r="F46" s="12" t="s">
@@ -2541,46 +2559,42 @@
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="14" t="s">
-        <v>241</v>
-      </c>
-      <c r="B47" s="14" t="s">
-        <v>242</v>
-      </c>
-      <c r="C47" s="14" t="s">
-        <v>243</v>
-      </c>
-      <c r="D47" s="14" t="s">
-        <v>244</v>
-      </c>
-      <c r="E47" s="15" t="s">
-        <v>245</v>
-      </c>
-      <c r="F47" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="G47" s="14" t="s">
-        <v>247</v>
-      </c>
-      <c r="H47" s="14" t="s">
-        <v>15</v>
-      </c>
+      <c r="A47" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="B47" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="E47" s="17" t="s">
+        <v>292</v>
+      </c>
+      <c r="F47" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="G47" s="12"/>
+      <c r="H47" s="12"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="14" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="E48" s="15" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="F48" s="14" t="s">
         <v>246</v>
@@ -2594,19 +2608,19 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="14" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E49" s="15" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F49" s="14" t="s">
         <v>246</v>
@@ -2620,19 +2634,19 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="14" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B50" s="14" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="F50" s="14" t="s">
         <v>246</v>
@@ -2646,19 +2660,19 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="14" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="E51" s="15" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="F51" s="14" t="s">
         <v>246</v>
@@ -2672,19 +2686,19 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="14" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="B52" s="14" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="F52" s="14" t="s">
         <v>246</v>
@@ -2698,19 +2712,19 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="14" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="B53" s="14" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="E53" s="15" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="F53" s="14" t="s">
         <v>246</v>
@@ -2724,19 +2738,19 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="14" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="B54" s="14" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="E54" s="15" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="F54" s="14" t="s">
         <v>246</v>
@@ -2745,12 +2759,40 @@
         <v>247</v>
       </c>
       <c r="H54" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="B55" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="C55" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="D55" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="E55" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="F55" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="G55" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="H55" s="14" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E28" r:id="rId1" xr:uid="{9D7F697B-04A3-43D8-834D-1DD935D30A27}"/>
+    <hyperlink ref="E46" r:id="rId2" xr:uid="{AD381954-74B6-4661-84EC-9487E2F47034}"/>
+    <hyperlink ref="E47" r:id="rId3" xr:uid="{7F578AA3-EA40-4432-9E0B-F9D624BADC2E}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/TalkTukTuk_Phrases.xlsx
+++ b/TalkTukTuk_Phrases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TOSHIBA\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1560E4F-7A3C-4E50-940E-AFF082ABE50A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33C5DF1B-E56B-4624-BD84-F3D2A279E5F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="420" yWindow="510" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="322">
   <si>
     <t>PhraseID</t>
   </si>
@@ -975,6 +975,18 @@
   </si>
   <si>
     <t>Msel menh</t>
+  </si>
+  <si>
+    <t>PHR-DAY-013</t>
+  </si>
+  <si>
+    <t>Morning</t>
+  </si>
+  <si>
+    <t>ព្រឹក</t>
+  </si>
+  <si>
+    <t>Proek</t>
   </si>
 </sst>
 </file>
@@ -1393,7 +1405,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -2923,40 +2935,40 @@
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="B67" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="C67" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="D67" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="E67" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="F67" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="G67" s="8" t="s">
+      <c r="A67" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="C67" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="F67" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="G67" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="8" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="E68" s="8" t="s">
         <v>181</v>
@@ -2970,16 +2982,16 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E69" s="8" t="s">
         <v>181</v>
@@ -2993,16 +3005,16 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E70" s="8" t="s">
         <v>181</v>
@@ -3016,16 +3028,16 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E71" s="8" t="s">
         <v>181</v>
@@ -3039,16 +3051,16 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="8" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E72" s="8" t="s">
         <v>181</v>
@@ -3062,16 +3074,16 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E73" s="8" t="s">
         <v>181</v>
@@ -3085,16 +3097,16 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="8" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E74" s="8" t="s">
         <v>181</v>
@@ -3108,16 +3120,16 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="B75" t="s">
-        <v>304</v>
+        <v>207</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>208</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>302</v>
+        <v>209</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>303</v>
+        <v>210</v>
       </c>
       <c r="E75" s="8" t="s">
         <v>181</v>
@@ -3126,6 +3138,29 @@
         <v>182</v>
       </c>
       <c r="G75" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="B76" t="s">
+        <v>304</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="E76" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="F76" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="G76" s="8" t="s">
         <v>13</v>
       </c>
     </row>

--- a/TalkTukTuk_Phrases.xlsx
+++ b/TalkTukTuk_Phrases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TOSHIBA\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33C5DF1B-E56B-4624-BD84-F3D2A279E5F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60843701-2E70-421C-BE41-0BE17BF67CD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="420" yWindow="510" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="338">
   <si>
     <t>PhraseID</t>
   </si>
@@ -987,6 +987,54 @@
   </si>
   <si>
     <t>Proek</t>
+  </si>
+  <si>
+    <t>សាច់មាន់</t>
+  </si>
+  <si>
+    <t>Sach Moan</t>
+  </si>
+  <si>
+    <t>Chicken</t>
+  </si>
+  <si>
+    <t>PHR-FOO-012</t>
+  </si>
+  <si>
+    <t>PHR-FOO-013</t>
+  </si>
+  <si>
+    <t>Beef</t>
+  </si>
+  <si>
+    <t>សាច់គោ</t>
+  </si>
+  <si>
+    <t>Sach Ko</t>
+  </si>
+  <si>
+    <t>PHR-FOO-014</t>
+  </si>
+  <si>
+    <t>Pork</t>
+  </si>
+  <si>
+    <t>សាច់ជ្រូក</t>
+  </si>
+  <si>
+    <t>Sach Chrou</t>
+  </si>
+  <si>
+    <t>PHR-FOO-015</t>
+  </si>
+  <si>
+    <t>Fish</t>
+  </si>
+  <si>
+    <t>ត្រី</t>
+  </si>
+  <si>
+    <t>Trey</t>
   </si>
 </sst>
 </file>
@@ -1405,7 +1453,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1854,109 +1902,109 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G20" s="4" t="s">
+      <c r="A20" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G21" s="4" t="s">
+      <c r="A21" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G22" s="4" t="s">
+      <c r="A22" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G23" s="4" t="s">
+      <c r="A23" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>80</v>
@@ -1970,16 +2018,16 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>286</v>
+        <v>82</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>287</v>
+        <v>83</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>288</v>
+        <v>84</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>289</v>
+        <v>85</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>80</v>
@@ -1993,16 +2041,16 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>290</v>
+        <v>86</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>291</v>
+        <v>87</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>292</v>
+        <v>88</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>293</v>
+        <v>89</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>80</v>
@@ -2016,16 +2064,16 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>294</v>
+        <v>90</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>295</v>
+        <v>91</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>296</v>
+        <v>92</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>297</v>
+        <v>93</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>80</v>
@@ -2039,16 +2087,16 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>298</v>
+        <v>94</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>299</v>
+        <v>95</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>300</v>
+        <v>96</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>301</v>
+        <v>97</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>80</v>
@@ -2061,109 +2109,109 @@
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="G29" s="5" t="s">
+      <c r="A29" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G29" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="G30" s="5" t="s">
+      <c r="A30" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G30" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="G31" s="5" t="s">
+      <c r="A31" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G31" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="G32" s="5" t="s">
+      <c r="A32" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G32" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>231</v>
+        <v>99</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>102</v>
@@ -2177,16 +2225,16 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>211</v>
+        <v>104</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>212</v>
+        <v>105</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>213</v>
+        <v>106</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>214</v>
+        <v>107</v>
       </c>
       <c r="E34" s="5" t="s">
         <v>102</v>
@@ -2200,16 +2248,16 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>227</v>
+        <v>108</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>228</v>
+        <v>109</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>229</v>
+        <v>110</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>230</v>
+        <v>111</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>102</v>
@@ -2223,16 +2271,16 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>232</v>
+        <v>112</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>233</v>
+        <v>113</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>234</v>
+        <v>114</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>235</v>
+        <v>115</v>
       </c>
       <c r="E36" s="5" t="s">
         <v>102</v>
@@ -2246,16 +2294,16 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>236</v>
+        <v>116</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>243</v>
+        <v>231</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>117</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>238</v>
+        <v>118</v>
       </c>
       <c r="E37" s="5" t="s">
         <v>102</v>
@@ -2269,16 +2317,16 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>239</v>
+        <v>211</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>241</v>
+        <v>212</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>213</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>242</v>
+        <v>214</v>
       </c>
       <c r="E38" s="5" t="s">
         <v>102</v>
@@ -2292,16 +2340,16 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>252</v>
+        <v>227</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>254</v>
+        <v>228</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>229</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>255</v>
+        <v>230</v>
       </c>
       <c r="E39" s="5" t="s">
         <v>102</v>
@@ -2315,16 +2363,16 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>256</v>
+        <v>232</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>258</v>
+        <v>233</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>234</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>259</v>
+        <v>235</v>
       </c>
       <c r="E40" s="5" t="s">
         <v>102</v>
@@ -2338,16 +2386,16 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>263</v>
+        <v>236</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>260</v>
+        <v>237</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>262</v>
+        <v>238</v>
       </c>
       <c r="E41" s="5" t="s">
         <v>102</v>
@@ -2361,16 +2409,16 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>264</v>
+        <v>240</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>265</v>
+        <v>241</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>266</v>
+        <v>242</v>
       </c>
       <c r="E42" s="5" t="s">
         <v>102</v>
@@ -2384,16 +2432,16 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>268</v>
+        <v>252</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>269</v>
+        <v>253</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>270</v>
+        <v>254</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>271</v>
+        <v>255</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>102</v>
@@ -2406,109 +2454,109 @@
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="G44" s="6" t="s">
+      <c r="A44" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G44" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="F45" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="G45" s="6" t="s">
+      <c r="A45" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G45" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="F46" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="G46" s="6" t="s">
+      <c r="A46" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G46" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="E47" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="F47" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="G47" s="6" t="s">
+      <c r="A47" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G47" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>122</v>
@@ -2522,16 +2570,16 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="E49" s="6" t="s">
         <v>122</v>
@@ -2545,16 +2593,16 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>122</v>
@@ -2568,16 +2616,16 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>122</v>
@@ -2591,16 +2639,16 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>122</v>
@@ -2614,16 +2662,16 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="E53" s="6" t="s">
         <v>122</v>
@@ -2637,16 +2685,16 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>272</v>
+        <v>139</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>285</v>
+        <v>140</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>284</v>
+        <v>141</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>122</v>
@@ -2659,109 +2707,109 @@
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="D55" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="F55" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="G55" s="7" t="s">
+      <c r="A55" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="F55" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="G55" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="E56" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="F56" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="G56" s="7" t="s">
+      <c r="A56" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="G56" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="F57" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="G57" s="7" t="s">
+      <c r="A57" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="F57" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="G57" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="F58" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="G58" s="7" t="s">
+      <c r="A58" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="G58" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="E59" s="7" t="s">
         <v>154</v>
@@ -2775,16 +2823,16 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E60" s="7" t="s">
         <v>154</v>
@@ -2798,16 +2846,16 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="E61" s="7" t="s">
         <v>154</v>
@@ -2821,16 +2869,16 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="E62" s="7" t="s">
         <v>154</v>
@@ -2844,16 +2892,16 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>215</v>
+        <v>165</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>216</v>
+        <v>166</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>217</v>
+        <v>167</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="E63" s="7" t="s">
         <v>154</v>
@@ -2867,16 +2915,16 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
-        <v>306</v>
+        <v>168</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>307</v>
+        <v>169</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>308</v>
+        <v>170</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>309</v>
+        <v>224</v>
       </c>
       <c r="E64" s="7" t="s">
         <v>154</v>
@@ -2890,16 +2938,16 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>310</v>
+        <v>171</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>311</v>
+        <v>172</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>312</v>
+        <v>173</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>313</v>
+        <v>225</v>
       </c>
       <c r="E65" s="7" t="s">
         <v>154</v>
@@ -2913,16 +2961,16 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>314</v>
+        <v>174</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="C66" s="11" t="s">
-        <v>316</v>
+        <v>175</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>176</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>317</v>
+        <v>226</v>
       </c>
       <c r="E66" s="7" t="s">
         <v>154</v>
@@ -2936,16 +2984,16 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>318</v>
+        <v>215</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="C67" s="11" t="s">
-        <v>320</v>
+        <v>216</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>217</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>321</v>
+        <v>218</v>
       </c>
       <c r="E67" s="7" t="s">
         <v>154</v>
@@ -2958,109 +3006,109 @@
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="B68" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="D68" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="E68" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="F68" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="G68" s="8" t="s">
+      <c r="A68" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="F68" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="G68" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="B69" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="C69" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="D69" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="E69" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="F69" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="G69" s="8" t="s">
+      <c r="A69" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="F69" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="G69" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="B70" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="C70" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="D70" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="E70" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="F70" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="G70" s="8" t="s">
+      <c r="A70" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="C70" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="E70" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="F70" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="G70" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="B71" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="C71" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="D71" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="E71" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="F71" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="G71" s="8" t="s">
+      <c r="A71" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="C71" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="E71" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="F71" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="G71" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="8" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="E72" s="8" t="s">
         <v>181</v>
@@ -3074,16 +3122,16 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="E73" s="8" t="s">
         <v>181</v>
@@ -3097,16 +3145,16 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="8" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="E74" s="8" t="s">
         <v>181</v>
@@ -3120,16 +3168,16 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="E75" s="8" t="s">
         <v>181</v>
@@ -3143,16 +3191,16 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="B76" t="s">
-        <v>304</v>
+        <v>195</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>196</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>302</v>
+        <v>197</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>303</v>
+        <v>198</v>
       </c>
       <c r="E76" s="8" t="s">
         <v>181</v>
@@ -3161,6 +3209,98 @@
         <v>182</v>
       </c>
       <c r="G76" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="D77" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="E77" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="F77" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="G77" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="B78" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="D78" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="G78" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="B79" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="D79" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="E79" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="G79" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="B80" t="s">
+        <v>304</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="D80" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="G80" s="8" t="s">
         <v>13</v>
       </c>
     </row>
